--- a/Web/TestCasesWeb/Categorias.xlsx
+++ b/Web/TestCasesWeb/Categorias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82F9801-EA10-495D-B723-0D74A6723DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56A12B6-975D-4C9E-9A96-3C4F5EF7E77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>Num</t>
   </si>
@@ -54,9 +54,6 @@
   <si>
     <t xml:space="preserve">1. The user clicks  "Categorias"
 </t>
-  </si>
-  <si>
-    <t>1. Categories home is not correctly.</t>
   </si>
   <si>
     <t>KO</t>
@@ -118,12 +115,6 @@
     <t>1. The categorie is deleted</t>
   </si>
   <si>
-    <t>1. The categorie is not deleted</t>
-  </si>
-  <si>
-    <t>No aparece ningún mensaje, pero creo que es porque está asociada a algún producto.</t>
-  </si>
-  <si>
     <t>Cancel the operation: Modify a category</t>
   </si>
   <si>
@@ -164,12 +155,6 @@
     <t>Delete a role</t>
   </si>
   <si>
-    <t>No se sabe muy bien como se modifica</t>
-  </si>
-  <si>
-    <t>No se sabe muy bien como se crea.</t>
-  </si>
-  <si>
     <t>1 .The role is created.</t>
   </si>
   <si>
@@ -206,18 +191,116 @@
     <t>CATEG010</t>
   </si>
   <si>
-    <t>No se avisa de que se va a borrar el rol
-Al borrar un rol, no se avisa/actualiza en la categoría</t>
-  </si>
-  <si>
     <t>BL</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">15/04/26: Fixed: moved "Printer Roles" block below the main categories table. Categories table is now the primary content of the page.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26: BLOQUEANTE: Al intentar crear un rol con un nombre muy largo, el sistema desconecta:categ_crearrol3.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26: BLOQUEANTE: Al crear una categoría con un nombre muy largo, se pierde la funcionalidad:categ_crearrol4.jpg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No aparece ningún mensaje, pero creo que es porque está asociada a algún producto.
+15/04/26: Fixed: removed disabled state from delete button (user had no feedback). handleDelete now shows a modal explaining why deletion is blocked if category has products. confirmDelete shows inline error if backend rejects.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26: Al borrar un rol con un nombre un poco largo, se sale del combo del mensaje.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No se avisa de que se va a borrar el rol
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Al borrar un rol, no se avisa/actualiza en la categoría
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">15/04/26: Fixed: ConfirmModal message now explicitly states that categories using this role will lose the association.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26: Al borrar el rol, sigue asociado a la categoría,y es un rol que no existe:categ_crearrol2.jpg</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +337,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,7 +384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -312,14 +401,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -667,7 +759,7 @@
     <col min="1" max="1" width="9.140625" style="5"/>
     <col min="2" max="2" width="15" style="5" customWidth="1"/>
     <col min="3" max="3" width="48" style="5" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" style="9" customWidth="1"/>
     <col min="5" max="6" width="33.42578125" style="5" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="5"/>
     <col min="8" max="8" width="91.42578125" style="5" bestFit="1" customWidth="1"/>
@@ -700,248 +792,242 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="F6" s="1"/>
       <c r="G6" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>43</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Web/TestCasesWeb/Categorias.xlsx
+++ b/Web/TestCasesWeb/Categorias.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56A12B6-975D-4C9E-9A96-3C4F5EF7E77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Web/TestCasesWeb/Categorias.xlsx
+++ b/Web/TestCasesWeb/Categorias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56A12B6-975D-4C9E-9A96-3C4F5EF7E77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B620E6-7EB5-46F1-8E0B-BBEA132366C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t>Num</t>
   </si>
@@ -44,12 +44,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>1. Categories home is correctly.</t>
-  </si>
-  <si>
-    <t>Categories page home</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks  "Categorias"
@@ -192,43 +186,6 @@
   </si>
   <si>
     <t>BL</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">15/04/26: Fixed: moved "Printer Roles" block below the main categories table. Categories table is now the primary content of the page.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15/04/26: BLOQUEANTE: Al intentar crear un rol con un nombre muy largo, el sistema desconecta:categ_crearrol3.jpg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15/04/26: BLOQUEANTE: Al crear una categoría con un nombre muy largo, se pierde la funcionalidad:categ_crearrol4.jpg</t>
-    </r>
   </si>
   <si>
     <r>
@@ -294,6 +251,24 @@
       </rPr>
       <t>15/04/26: Al borrar el rol, sigue asociado a la categoría,y es un rol que no existe:categ_crearrol2.jpg</t>
     </r>
+  </si>
+  <si>
+    <t>Categories page.</t>
+  </si>
+  <si>
+    <t>1. Categories page is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/04/26: Fixed: moved "Printer Roles" block below the main categories table. Categories table is now the primary content of the page.
+</t>
+  </si>
+  <si>
+    <t>15/04/26: BLOQUEANTE: Al intentar crear un rol con un nombre muy largo, el sistema desconecta:categ_crearrol3.jpg
+15/04/26: BLOQUEANTE: Al crear una categoría con un nombre muy largo, se pierde la funcionalidad:categ_crearrol4.jpg
+11/05/26: Al pusar, crear categoría sin introducir nada en el campo no dice nada. Debería salir un mensaje como en el POS q muestra: "Introduce un nombre de rol válido"</t>
+  </si>
+  <si>
+    <t>BLOQUEANTE: Internal server error, no crea la categoría: CATEG005.jpg</t>
   </si>
 </sst>
 </file>
@@ -384,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -412,6 +387,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -792,28 +770,28 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="3" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -821,42 +799,44 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -865,25 +845,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -891,23 +871,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -915,22 +895,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -939,70 +919,72 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="7"/>
+        <v>9</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H10" s="7"/>
     </row>
@@ -1011,23 +993,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Web/TestCasesWeb/Categorias.xlsx
+++ b/Web/TestCasesWeb/Categorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B620E6-7EB5-46F1-8E0B-BBEA132366C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0E989E-1DD3-4DEF-BB88-0F8391097C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Num</t>
   </si>
@@ -71,19 +71,7 @@
 3. The user clicks "Crear"</t>
   </si>
   <si>
-    <t>Create a categorie with mandatory parameters.</t>
-  </si>
-  <si>
     <t>1. The categorie is created</t>
-  </si>
-  <si>
-    <t>Create a categorie with all parameters.</t>
-  </si>
-  <si>
-    <t>Modify a category</t>
-  </si>
-  <si>
-    <t>Delete a category</t>
   </si>
   <si>
     <t>CATEG005</t>
@@ -109,12 +97,6 @@
     <t>1. The categorie is deleted</t>
   </si>
   <si>
-    <t>Cancel the operation: Modify a category</t>
-  </si>
-  <si>
-    <t>Cancel the operation: Delete a category</t>
-  </si>
-  <si>
     <t>1. The user selects a category
 2. The  user modify a field
 3. The user clicks "Cancelar"</t>
@@ -128,25 +110,7 @@
     <t>Al colocarte encima del lapiz, no sale la etiqueta "editar" como al colocarte en el icono de papelera, sale "Eliminar"</t>
   </si>
   <si>
-    <t>1.The icon has not a label</t>
-  </si>
-  <si>
-    <t>1 .The category is not modified.</t>
-  </si>
-  <si>
-    <t>1 .The category is not deleted.</t>
-  </si>
-  <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>Create a role</t>
-  </si>
-  <si>
-    <t>Modify a role</t>
-  </si>
-  <si>
-    <t>Delete a role</t>
   </si>
   <si>
     <t>1 .The role is created.</t>
@@ -156,10 +120,6 @@
 2 .The user mofidies the name of the role</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user clicks the garbage of the role
-</t>
-  </si>
-  <si>
     <t>1 .The role is deleted.</t>
   </si>
   <si>
@@ -182,38 +142,7 @@
     <t>CATEG009</t>
   </si>
   <si>
-    <t>CATEG010</t>
-  </si>
-  <si>
     <t>BL</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">No aparece ningún mensaje, pero creo que es porque está asociada a algún producto.
-15/04/26: Fixed: removed disabled state from delete button (user had no feedback). handleDelete now shows a modal explaining why deletion is blocked if category has products. confirmDelete shows inline error if backend rejects.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>15/04/26: Al borrar un rol con un nombre un poco largo, se sale del combo del mensaje.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
   </si>
   <si>
     <r>
@@ -253,9 +182,6 @@
     </r>
   </si>
   <si>
-    <t>Categories page.</t>
-  </si>
-  <si>
     <t>1. Categories page is correctly.</t>
   </si>
   <si>
@@ -263,12 +189,98 @@
 </t>
   </si>
   <si>
+    <t>Categories page</t>
+  </si>
+  <si>
+    <t>Categories: Create, mandatory parameters.</t>
+  </si>
+  <si>
+    <t>Categories: Create, all parameters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories: Modify </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories: Delete </t>
+  </si>
+  <si>
+    <t>Categories: Modify, cancel</t>
+  </si>
+  <si>
+    <t>Categories: Create, cancel</t>
+  </si>
+  <si>
+    <t>1. The user clicks  "Categorias"
+2. The user clicks "Nueva categoría"
+3. The user clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1 .The operation is cancelled</t>
+  </si>
+  <si>
+    <t>Categories: Delete, cancel</t>
+  </si>
+  <si>
+    <t>Categories: Create a role</t>
+  </si>
+  <si>
+    <t>Categories: Modify a role</t>
+  </si>
+  <si>
+    <t>Categories: Delete a role</t>
+  </si>
+  <si>
+    <t>CATEG011</t>
+  </si>
+  <si>
+    <t>CATEG012</t>
+  </si>
+  <si>
+    <t>Categories: Delete a role,cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the garbage of the role
+2. Clicks "Eliminar"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks the garbage of the role
+2. Clicks "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>CATEG013</t>
+  </si>
+  <si>
     <t>15/04/26: BLOQUEANTE: Al intentar crear un rol con un nombre muy largo, el sistema desconecta:categ_crearrol3.jpg
 15/04/26: BLOQUEANTE: Al crear una categoría con un nombre muy largo, se pierde la funcionalidad:categ_crearrol4.jpg
-11/05/26: Al pusar, crear categoría sin introducir nada en el campo no dice nada. Debería salir un mensaje como en el POS q muestra: "Introduce un nombre de rol válido"</t>
-  </si>
-  <si>
-    <t>BLOQUEANTE: Internal server error, no crea la categoría: CATEG005.jpg</t>
+11/05/26: Al pusar, crear categoría sin introducir nada en el campo no dice nada. Debería salir un mensaje como en el POS q muestra: "Introduce un nombre de rol válido"
+19/05/26: Error al poner un nombre muy largo: CATEG008.jpg</t>
+  </si>
+  <si>
+    <t>19/05/26: Modificando el nombre del rol, y poniendo uno muy largo ha falladado, CATEG008.jpg</t>
+  </si>
+  <si>
+    <t>BLOQUEANTE: Internal server error, no crea la categoría: CATEG005.jpg
+19/05/26: Se crea la categoría</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No aparece ningún mensaje, pero creo que es porque está asociada a algún producto.
+15/04/26: Fixed: removed disabled state from delete button (user had no feedback). handleDelete now shows a modal explaining why deletion is blocked if category has products. confirmDelete shows inline error if backend rejects.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26: Al borrar un rol con un nombre un poco largo, se sale del combo del mensaje.
+19/05/26: No se puede borrar un rol con nombre largo, xq no se muestran las opciones Cancelar/Eliminar: CATEG009.jpg</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -388,7 +400,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -731,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -778,20 +790,20 @@
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -802,20 +814,20 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="6" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -826,17 +838,17 @@
         <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -848,46 +860,42 @@
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -895,126 +903,172 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" s="8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" s="6" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" s="6" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="6" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="D12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G11">
+  <conditionalFormatting sqref="G2:G13">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
